--- a/medical_application_forms/030_patient_intake_form--medical_application_forms.xlsx
+++ b/medical_application_forms/030_patient_intake_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'new_patient'}</t>
+          <t>new_patient</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'New Patient'}</t>
+          <t>New Patient</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'existing_patient'}</t>
+          <t>existing_patient</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Existing Patient'}</t>
+          <t>Existing Patient</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unknown_patient'}</t>
+          <t>unknown_patient</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unknown Patient'}</t>
+          <t>Unknown Patient</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dermatology'}</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dermatology'}</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'endocrinology'}</t>
+          <t>endocrinology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Endocrinology'}</t>
+          <t>Endocrinology</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'gastroenterology'}</t>
+          <t>gastroenterology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Gastroenterology'}</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'general_practice'}</t>
+          <t>general_practice</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'General Practice'}</t>
+          <t>General Practice</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'nephrology'}</t>
+          <t>nephrology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Nephrology'}</t>
+          <t>Nephrology</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medicare'}</t>
+          <t>medicare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medicare'}</t>
+          <t>Medicare</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medicaid'}</t>
+          <t>medicaid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medicaid'}</t>
+          <t>Medicaid</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'tricare'}</t>
+          <t>tricare</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Tricare'}</t>
+          <t>Tricare</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
